--- a/total_de_gastos.xlsx
+++ b/total_de_gastos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -433,6 +433,11 @@
 </t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -556,6 +561,50 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>Lazer</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Corte de Cabelo</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Lazer</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>06/11/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Carne Para Hambúrguer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Lazer</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>06/11/2025</t>
         </is>
       </c>
     </row>

--- a/total_de_gastos.xlsx
+++ b/total_de_gastos.xlsx
@@ -1,128 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Sheet"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Novembro" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
-  <si>
-    <t>Descrição</t>
-  </si>
-  <si>
-    <t>Valor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Critério
-</t>
-  </si>
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>Recarga do cartão</t>
-  </si>
-  <si>
-    <t>20.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Essencial
-</t>
-  </si>
-  <si>
-    <t>Mercado</t>
-  </si>
-  <si>
-    <t>125.00</t>
-  </si>
-  <si>
-    <t>Lanche</t>
-  </si>
-  <si>
-    <t>55.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lazer
-</t>
-  </si>
-  <si>
-    <t>Uber</t>
-  </si>
-  <si>
-    <t>25.00</t>
-  </si>
-  <si>
-    <t>Aluguel</t>
-  </si>
-  <si>
-    <t>400.00</t>
-  </si>
-  <si>
-    <t>Luz</t>
-  </si>
-  <si>
-    <t>53.50</t>
-  </si>
-  <si>
-    <t>Pastel</t>
-  </si>
-  <si>
-    <t>17.50</t>
-  </si>
-  <si>
-    <t>Lazer</t>
-  </si>
-  <si>
-    <t>Corte de Cabelo</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>06/11/2025</t>
-  </si>
-  <si>
-    <t>Carne Para Hambúrguer</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>Pizza</t>
-  </si>
-  <si>
-    <t>21.50</t>
-  </si>
-  <si>
-    <t>10/11/2025</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -141,24 +47,86 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -446,160 +414,255 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="1"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="1"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="1"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="1"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="1"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="1"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>28</v>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Descrição</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Critério
+</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18.75" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Recarga do cartão</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Essencial
+</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Mercado</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Essencial
+</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Lanche</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lazer
+</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Essencial
+</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="18.75" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Aluguel</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>400.00</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Essencial
+</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="18.75" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Luz</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>53.50</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Essencial
+</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="18.75" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Pastel</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>17.50</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Lazer</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="18.75" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Corte de Cabelo</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Lazer</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>06/11/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18.75" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Carne Para Hambúrguer</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Lazer</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06/11/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18.75" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Pizza</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>21.50</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Lazer</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/total_de_gastos.xlsx
+++ b/total_de_gastos.xlsx
@@ -6,8 +6,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Novembro" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Novembro" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,253 +415,57 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Descrição</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Critério
-</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18.75" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Recarga do cartão</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Essencial
-</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Mercado</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Essencial
-</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n"/>
-    </row>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Lanche</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lazer
-</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n"/>
-    </row>
-    <row r="5" ht="18.75" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Uber</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>25.00</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Essencial
-</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n"/>
-    </row>
-    <row r="6" ht="18.75" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Aluguel</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>400.00</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Essencial
-</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n"/>
-    </row>
-    <row r="7" ht="18.75" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Luz</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>53.50</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Essencial
-</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n"/>
-    </row>
-    <row r="8" ht="18.75" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Pastel</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>17.50</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Lazer</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n"/>
-    </row>
-    <row r="9" ht="18.75" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Corte de Cabelo</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Lazer</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>06/11/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18.75" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Carne Para Hambúrguer</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Lazer</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>06/11/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18.75" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Pizza</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>21.50</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Lazer</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>10/11/2025</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Descrição</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tipo de gasto</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Cartão do ônibus</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Essencial</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>12/11/2025</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/total_de_gastos.xlsx
+++ b/total_de_gastos.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,28 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>12/11/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aluguel Bike</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>10.70</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Lazer</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>15/11/2025</t>
         </is>
       </c>
     </row>

--- a/total_de_gastos.xlsx
+++ b/total_de_gastos.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,6 +484,28 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>15/11/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Pastel</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>07.99</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Lazer</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>17/11/2025</t>
         </is>
       </c>
     </row>

--- a/total_de_gastos.xlsx
+++ b/total_de_gastos.xlsx
@@ -415,101 +415,107 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Descrição</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Tipo de gasto</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="18.75" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Cartão do ônibus</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>30.00</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Essencial</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>12/11/2025</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Aluguel Bike</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>10.70</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Lazer</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>15/11/2025</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Pastel</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>07.99</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Lazer</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>17/11/2025</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/total_de_gastos.xlsx
+++ b/total_de_gastos.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Novembro" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -45,14 +45,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -134,10 +129,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -175,71 +170,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -267,7 +262,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -290,11 +285,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -303,13 +298,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -319,7 +314,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -328,7 +323,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -337,7 +332,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -345,10 +340,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -418,103 +413,125 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
-    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
+    <col width="13.5703125" bestFit="1" customWidth="1" style="1" min="1" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="18.75" customHeight="1" s="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Descrição</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Tipo de gasto</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18.75" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="18.75" customHeight="1" s="1">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Cartão do ônibus</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>30.00</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Essencial</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>12/11/2025</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1" s="1">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Aluguel Bike</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>10.70</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Lazer</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>15/11/2025</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="4" ht="18.75" customHeight="1" s="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Pastel</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>07.99</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Lazer</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>17/11/2025</t>
         </is>
       </c>
     </row>
+    <row r="5" ht="18.75" customHeight="1" s="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Cartão Meia Passagem</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Transporte</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>19/11/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18.75" customHeight="1" s="1"/>
+    <row r="7" ht="18.75" customHeight="1" s="1"/>
+    <row r="8" ht="18.75" customHeight="1" s="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/total_de_gastos.xlsx
+++ b/total_de_gastos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5703125" bestFit="1" customWidth="1" style="1" min="1" max="4"/>
@@ -529,9 +529,72 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="18.75" customHeight="1" s="1"/>
-    <row r="7" ht="18.75" customHeight="1" s="1"/>
-    <row r="8" ht="18.75" customHeight="1" s="1"/>
+    <row r="6" ht="18.75" customHeight="1" s="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Mercado</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Essencial</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>20/11/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18.75" customHeight="1" s="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Pizza em Zé vaqueiro</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Lazer</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>20/11/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18.75" customHeight="1" s="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Hamburguer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>26.00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Lazer</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>22/11/2025</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/total_de_gastos.xlsx
+++ b/total_de_gastos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5703125" bestFit="1" customWidth="1" style="1" min="1" max="4"/>
@@ -554,12 +554,12 @@
     <row r="7" ht="18.75" customHeight="1" s="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pizza em Zé vaqueiro</t>
+          <t>Pizza em Zé Vaqueiro</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23.00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -569,29 +569,73 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>23/11/2025</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1" s="1">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>30.00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Transporte</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>25/11/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Hamburguer</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>26.00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>27.00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Lazer</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>22/11/2025</t>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>25/11/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Padaria</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Essencial</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>25/11/2025</t>
         </is>
       </c>
     </row>

--- a/total_de_gastos.xlsx
+++ b/total_de_gastos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.5703125" bestFit="1" customWidth="1" style="1" min="1" max="4"/>
@@ -639,6 +639,50 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Meia Passagem</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Transporte</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>26/11/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Mercado</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Essencial</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>27/11/2025</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/total_de_gastos.xlsx
+++ b/total_de_gastos.xlsx
@@ -7,6 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Novembro" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dezembro" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -414,7 +415,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="13.5703125" bestFit="1" customWidth="1" style="1" min="1" max="4"/>
   </cols>
@@ -686,4 +687,194 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Descrição</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tipo de gasto</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Padaria</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Essencial</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>04/12/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Mercado</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Essencial</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ações da Meliuz</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Investimentos</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Burguer King</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Lazer</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aluguel</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Essencial</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Essencial</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Luz</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>76.50</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Essencial</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/total_de_gastos.xlsx
+++ b/total_de_gastos.xlsx
@@ -695,7 +695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -811,34 +811,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Açaí</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Essencial</t>
+          <t>Lazer</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>07/12/2025</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Internet</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>400</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -848,29 +848,117 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>07/12/2025</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Google Fotos</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Essencial</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Transporte</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Luz</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>76.50</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Essencial</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>05/12/2025</t>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Essencial</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>08/12/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Pizza</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Lazer</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>09/12/2025</t>
         </is>
       </c>
     </row>

--- a/total_de_gastos.xlsx
+++ b/total_de_gastos.xlsx
@@ -695,7 +695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -962,6 +962,28 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Netflix</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Lazer</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>30/12/2025</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/total_de_gastos.xlsx
+++ b/total_de_gastos.xlsx
@@ -1,51 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Plan1"/>
-    <sheet r:id="rId2" sheetId="2" name="Janeiro"/>
+    <sheet name="Plan1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Janeiro" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>Descrição</t>
-  </si>
-  <si>
-    <t>Valor</t>
-  </si>
-  <si>
-    <t>Tipo de gasto</t>
-  </si>
-  <si>
-    <t>Data</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -64,24 +47,86 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -369,43 +414,53 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
+    <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Descrição</t>
+        </is>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Tipo de gasto</t>
+        </is>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/total_de_gastos.xlsx
+++ b/total_de_gastos.xlsx
@@ -6,8 +6,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Plan1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Janeiro" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Janeiro" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fevereiro" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,21 +419,8 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
@@ -466,4 +453,172 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Descrição</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tipo de gasto</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>teste</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Essencial</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>04/02/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>reeeeeeeeetes</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Alimentação</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>04/02/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>teste</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Lazer</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>04/02/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Investimentos</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>04/02/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Transporte</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>04/02/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>zzz</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1346</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Auto Cuidado</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>04/02/2026</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/total_de_gastos.xlsx
+++ b/total_de_gastos.xlsx
@@ -8,6 +8,7 @@
   <sheets>
     <sheet name="Janeiro" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Fevereiro" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Março" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,7 +421,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
@@ -621,4 +622,40 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Descrição</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tipo de gasto</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>